--- a/artfynd/A 1697-2023 artfynd.xlsx
+++ b/artfynd/A 1697-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1697-2023 artfynd.xlsx
+++ b/artfynd/A 1697-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97990652</v>
+        <v>130959135</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Riksten, Srm</t>
+          <t>Lida, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666623.2667255496</v>
+        <v>666483</v>
       </c>
       <c r="R2" t="n">
-        <v>6562440.967860853</v>
+        <v>6562307</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-10-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-10-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sverige. Södermanland: Botkyrka sn, Riksten, 300 m. V om Rikstens huvudbyggnad, skogsbryn vid grusväg. 10I 2e 2706. 6562700, 1620661.</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,62 +757,51 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>L60698</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Anna-Sara Liman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Fingal Gyllang</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Sand- och åsbarrskogar i Stockholms län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97990646</v>
+        <v>97990652</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666623.2667255496</v>
+        <v>666623</v>
       </c>
       <c r="R3" t="n">
-        <v>6562440.967860853</v>
+        <v>6562441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,24 +844,14 @@
           <t>2003-10-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2003-10-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sverige. Södermanland: Botkyrka sn, Riksten, 300 m. V om Rikstens huvudbyggnad, skogsbryn vid grusväg. 10I 2E 2706. 6562700, 1620661.</t>
+          <t>Sverige. Södermanland: Botkyrka sn, Riksten, 300 m. V om Rikstens huvudbyggnad, skogsbryn vid grusväg. 10I 2e 2706. 6562700, 1620661.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +870,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>L60721</t>
+          <t>L60698</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -926,6 +885,118 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97990646</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Riksten, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>666623</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6562441</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2003-10-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2003-10-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sverige. Södermanland: Botkyrka sn, Riksten, 300 m. V om Rikstens huvudbyggnad, skogsbryn vid grusväg. 10I 2E 2706. 6562700, 1620661.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>L60721</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1697-2023 artfynd.xlsx
+++ b/artfynd/A 1697-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Sand- och åsbarrskogar i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130959135</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97990652</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97990646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>